--- a/data/out/variants/v6_no_econ_fuel_cost/summary_v6_no_econ_fuel_cost.xlsx
+++ b/data/out/variants/v6_no_econ_fuel_cost/summary_v6_no_econ_fuel_cost.xlsx
@@ -523,19 +523,19 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.448532257583551</v>
+        <v>0.4485322575835602</v>
       </c>
       <c r="F2" t="n">
-        <v>219.7333565470926</v>
+        <v>219.7333565470897</v>
       </c>
       <c r="G2" t="n">
-        <v>138579.3018236815</v>
+        <v>138579.3018236792</v>
       </c>
       <c r="H2" t="n">
-        <v>372.262409898826</v>
+        <v>372.2624098988229</v>
       </c>
       <c r="I2" t="n">
-        <v>71.35981934459809</v>
+        <v>71.3598193445969</v>
       </c>
       <c r="J2" t="n">
         <v>48192</v>
@@ -547,7 +547,7 @@
         <v>9639</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03131651878356934</v>
+        <v>0.03100061416625977</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -574,19 +574,19 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>0.4485181172451238</v>
+        <v>0.4485180480067537</v>
       </c>
       <c r="F3" t="n">
-        <v>219.739654902691</v>
+        <v>219.7397519947465</v>
       </c>
       <c r="G3" t="n">
-        <v>138582.8551742695</v>
+        <v>138582.8725733017</v>
       </c>
       <c r="H3" t="n">
-        <v>372.2671825104511</v>
+        <v>372.267205879462</v>
       </c>
       <c r="I3" t="n">
-        <v>71.36290560684017</v>
+        <v>71.36302762987839</v>
       </c>
       <c r="J3" t="n">
         <v>48192</v>
@@ -598,7 +598,7 @@
         <v>9639</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02504801750183105</v>
+        <v>0.02400016784667969</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -625,19 +625,19 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>0.4481399277244127</v>
+        <v>0.448051402282922</v>
       </c>
       <c r="F4" t="n">
-        <v>221.2162365746235</v>
+        <v>221.2178644493547</v>
       </c>
       <c r="G4" t="n">
-        <v>138677.8910860847</v>
+        <v>138700.1368004426</v>
       </c>
       <c r="H4" t="n">
-        <v>372.3948053962147</v>
+        <v>372.4246726526623</v>
       </c>
       <c r="I4" t="n">
-        <v>72.92113051470014</v>
+        <v>72.90982367941453</v>
       </c>
       <c r="J4" t="n">
         <v>48192</v>
@@ -649,7 +649,7 @@
         <v>9639</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0908348560333252</v>
+        <v>0.2332222461700439</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.4324241116292108</v>
+        <v>0.4324014420441871</v>
       </c>
       <c r="F5" t="n">
-        <v>226.8054762803715</v>
+        <v>226.8190211434614</v>
       </c>
       <c r="G5" t="n">
-        <v>142627.146236566</v>
+        <v>142632.8429165775</v>
       </c>
       <c r="H5" t="n">
-        <v>377.6600935187168</v>
+        <v>377.6676355164386</v>
       </c>
       <c r="I5" t="n">
-        <v>74.67852164290663</v>
+        <v>74.6928320368561</v>
       </c>
       <c r="J5" t="n">
         <v>48192</v>
@@ -704,7 +704,7 @@
         <v>9639</v>
       </c>
       <c r="M5" t="n">
-        <v>3.400393009185791</v>
+        <v>9.864825248718262</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>-165.5235411953343</v>
+        <v>-165.4740197901414</v>
       </c>
     </row>
     <row r="6">
@@ -740,7 +740,7 @@
         <v>-0.06647936739763871</v>
       </c>
       <c r="F6" t="n">
-        <v>301.059758509044</v>
+        <v>301.0597585090441</v>
       </c>
       <c r="G6" t="n">
         <v>267997.4815856392</v>
@@ -749,7 +749,7 @@
         <v>517.6847318452025</v>
       </c>
       <c r="I6" t="n">
-        <v>60.33254487410181</v>
+        <v>60.33254487410183</v>
       </c>
       <c r="J6" t="n">
         <v>48192</v>
@@ -761,7 +761,7 @@
         <v>9639</v>
       </c>
       <c r="M6" t="n">
-        <v>1.534134149551392</v>
+        <v>4.631065845489502</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -794,19 +794,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.1207442000415322</v>
+        <v>0.144685504810898</v>
       </c>
       <c r="F7" t="n">
-        <v>268.6389115562665</v>
+        <v>264.0381856886646</v>
       </c>
       <c r="G7" t="n">
-        <v>220949.7410469618</v>
+        <v>214933.4883371501</v>
       </c>
       <c r="H7" t="n">
-        <v>470.0529130289077</v>
+        <v>463.6091978565029</v>
       </c>
       <c r="I7" t="n">
-        <v>59.68749217131761</v>
+        <v>59.32143556321044</v>
       </c>
       <c r="J7" t="n">
         <v>48192</v>
@@ -818,7 +818,7 @@
         <v>9639</v>
       </c>
       <c r="M7" t="n">
-        <v>275.6125435829163</v>
+        <v>750.764461517334</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>-152.8935454493206</v>
+        <v>-152.8291173312737</v>
       </c>
     </row>
     <row r="8">
@@ -847,23 +847,23 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'learning_rate': 0.05, 'max_depth': 3, 'n_estimators': 200}</t>
+          <t>{'learning_rate': 0.1, 'max_depth': 3, 'n_estimators': 100}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.4322646514383088</v>
+        <v>0.4136357051631334</v>
       </c>
       <c r="F8" t="n">
-        <v>190.8679997549796</v>
+        <v>195.9108983554118</v>
       </c>
       <c r="G8" t="n">
-        <v>142667.2172692379</v>
+        <v>147348.5180416322</v>
       </c>
       <c r="H8" t="n">
-        <v>377.7131415098472</v>
+        <v>383.860024021299</v>
       </c>
       <c r="I8" t="n">
-        <v>37.68304792531617</v>
+        <v>37.46402237950171</v>
       </c>
       <c r="J8" t="n">
         <v>48192</v>
@@ -875,7 +875,7 @@
         <v>9639</v>
       </c>
       <c r="M8" t="n">
-        <v>182.3153781890869</v>
+        <v>416.5025157928467</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>-148.2940608280315</v>
+        <v>-148.4484108802963</v>
       </c>
     </row>
     <row r="9">
@@ -908,19 +908,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.06927821820898339</v>
+        <v>0.05532336883228584</v>
       </c>
       <c r="F9" t="n">
-        <v>309.2061717689223</v>
+        <v>313.8575742899937</v>
       </c>
       <c r="G9" t="n">
-        <v>233882.718411645</v>
+        <v>237389.4571289516</v>
       </c>
       <c r="H9" t="n">
-        <v>483.6142247821553</v>
+        <v>487.226289447677</v>
       </c>
       <c r="I9" t="n">
-        <v>83.58812207542054</v>
+        <v>85.82272845521874</v>
       </c>
       <c r="J9" t="n">
         <v>48192</v>
@@ -932,7 +932,7 @@
         <v>9639</v>
       </c>
       <c r="M9" t="n">
-        <v>120.3765571117401</v>
+        <v>269.8233661651611</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>-249.452918469298</v>
+        <v>-246.8016732947362</v>
       </c>
     </row>
     <row r="10">
@@ -965,19 +965,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.3986895625892594</v>
+        <v>0.3856157719542602</v>
       </c>
       <c r="F10" t="n">
-        <v>246.0629955685978</v>
+        <v>248.0918758614557</v>
       </c>
       <c r="G10" t="n">
-        <v>151104.3605751753</v>
+        <v>154389.6964870245</v>
       </c>
       <c r="H10" t="n">
-        <v>388.7214434208322</v>
+        <v>392.9245429939755</v>
       </c>
       <c r="I10" t="n">
-        <v>70.12488172904709</v>
+        <v>69.37621573930186</v>
       </c>
       <c r="J10" t="n">
         <v>48192</v>
@@ -989,7 +989,7 @@
         <v>9639</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8028135299682617</v>
+        <v>1.911223411560059</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="O10" t="n">
-        <v>-241.0800594158667</v>
+        <v>-241.3457731305625</v>
       </c>
     </row>
     <row r="11">
@@ -1018,23 +1018,23 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 302, 'learning_rate': 0.08260041138848145, 'max_depth': 3, 'subsample': 0.9566635916548611, 'colsample_bytree': 0.6009253485513868}</t>
+          <t>{'n_estimators': 337, 'learning_rate': 0.04591735385719001, 'max_depth': 3, 'subsample': 0.8331530640485033, 'colsample_bytree': 0.9991572144432869}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.3438067874325963</v>
+        <v>0.425636240084861</v>
       </c>
       <c r="F11" t="n">
-        <v>219.9879870457896</v>
+        <v>192.3853165246874</v>
       </c>
       <c r="G11" t="n">
-        <v>164895.9499617635</v>
+        <v>144332.8824512773</v>
       </c>
       <c r="H11" t="n">
-        <v>406.073823290499</v>
+        <v>379.9116771715201</v>
       </c>
       <c r="I11" t="n">
-        <v>42.8846130446268</v>
+        <v>37.48090036581188</v>
       </c>
       <c r="J11" t="n">
         <v>48192</v>
@@ -1046,7 +1046,7 @@
         <v>9639</v>
       </c>
       <c r="M11" t="n">
-        <v>43.30528903007507</v>
+        <v>79.78460240364075</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1073,23 +1073,23 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 581, 'learning_rate': 0.015903622735411446, 'num_leaves': 31, 'min_child_samples': 48}</t>
+          <t>{'n_estimators': 459, 'learning_rate': 0.019493523730913214, 'num_leaves': 71, 'min_child_samples': 43}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.2719508799114543</v>
+        <v>0.2174212925796756</v>
       </c>
       <c r="F12" t="n">
-        <v>236.9924594266984</v>
+        <v>246.620837380351</v>
       </c>
       <c r="G12" t="n">
-        <v>182952.747722143</v>
+        <v>196655.5839171653</v>
       </c>
       <c r="H12" t="n">
-        <v>427.7297601548705</v>
+        <v>443.458660888662</v>
       </c>
       <c r="I12" t="n">
-        <v>51.14574687158038</v>
+        <v>53.81384328577785</v>
       </c>
       <c r="J12" t="n">
         <v>48192</v>
@@ -1101,7 +1101,7 @@
         <v>9639</v>
       </c>
       <c r="M12" t="n">
-        <v>127.0487096309662</v>
+        <v>288.5815317630768</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1128,23 +1128,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'iterations': 332, 'learning_rate': 0.053148496685908944, 'depth': 4}</t>
+          <t>{'iterations': 316, 'learning_rate': 0.03251884186296887, 'depth': 4}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.3581518872680498</v>
+        <v>0.3572226719084325</v>
       </c>
       <c r="F13" t="n">
-        <v>218.2153362571899</v>
+        <v>216.8983362864909</v>
       </c>
       <c r="G13" t="n">
-        <v>161291.1445182441</v>
+        <v>161524.6486851703</v>
       </c>
       <c r="H13" t="n">
-        <v>401.610687754004</v>
+        <v>401.9012922163479</v>
       </c>
       <c r="I13" t="n">
-        <v>43.61976120994191</v>
+        <v>42.33553096030645</v>
       </c>
       <c r="J13" t="n">
         <v>48192</v>
@@ -1156,7 +1156,7 @@
         <v>9639</v>
       </c>
       <c r="M13" t="n">
-        <v>70.12607765197754</v>
+        <v>247.5982511043549</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1183,23 +1183,23 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'max_depth': 10, 'min_samples_split': 2, 'n_estimators': 500}</t>
+          <t>{'max_depth': None, 'min_samples_split': 2, 'n_estimators': 500}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.2468876686282216</v>
+        <v>0.2339858746906787</v>
       </c>
       <c r="F14" t="n">
-        <v>249.9569394656917</v>
+        <v>254.4859163875926</v>
       </c>
       <c r="G14" t="n">
-        <v>189250.9262989543</v>
+        <v>192493.0408572843</v>
       </c>
       <c r="H14" t="n">
-        <v>435.0297993229364</v>
+        <v>438.740288618773</v>
       </c>
       <c r="I14" t="n">
-        <v>55.48220068801844</v>
+        <v>57.22434527598893</v>
       </c>
       <c r="J14" t="n">
         <v>48192</v>
@@ -1211,7 +1211,7 @@
         <v>9639</v>
       </c>
       <c r="M14" t="n">
-        <v>50.99415445327759</v>
+        <v>157.9747486114502</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>-163.0802230325746</v>
+        <v>-162.1388503782532</v>
       </c>
     </row>
     <row r="15">
@@ -1268,7 +1268,7 @@
         <v>9639</v>
       </c>
       <c r="M15" t="n">
-        <v>9.937774896621704</v>
+        <v>29.47991180419922</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="O15" t="n">
-        <v>-147.2210481841708</v>
+        <v>-147.190066366052</v>
       </c>
     </row>
     <row r="16">
@@ -1301,19 +1301,19 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6184699961653531</v>
+        <v>0.5866994303552509</v>
       </c>
       <c r="F16" t="n">
-        <v>181.6634121780346</v>
+        <v>185.0878857349718</v>
       </c>
       <c r="G16" t="n">
-        <v>95875.3477121146</v>
+        <v>103859.0292402764</v>
       </c>
       <c r="H16" t="n">
-        <v>309.6374455909921</v>
+        <v>322.2716699312498</v>
       </c>
       <c r="I16" t="n">
-        <v>44.15569082957252</v>
+        <v>40.37794776790827</v>
       </c>
       <c r="J16" t="n">
         <v>48192</v>
@@ -1325,7 +1325,7 @@
         <v>9639</v>
       </c>
       <c r="M16" t="n">
-        <v>2449.289284229279</v>
+        <v>4371.79407286644</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>-180.9636195291112</v>
+        <v>-179.519204640765</v>
       </c>
     </row>
   </sheetData>
